--- a/宗门论道_开发管理工具包.xlsx
+++ b/宗门论道_开发管理工具包.xlsx
@@ -7,9 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="1.设计思路与玩法" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2.开发主表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="3.进度统计" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="0.开发阶段规划" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="1.设计思路与玩法" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2.开发主表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="3.进度统计" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -99,8 +100,32 @@
       <color rgb="00C0392B"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00117A65"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="002C3E50"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00B7950B"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="18">
+  <fills count="20">
     <fill>
       <patternFill/>
     </fill>
@@ -187,8 +212,18 @@
         <fgColor rgb="00D5D8DC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0027AE60"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF9E7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -210,11 +245,55 @@
         <color rgb="00D5D8DC"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D5D8DC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D5D8DC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D5D8DC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D5D8DC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D5D8DC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D5D8DC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D5D8DC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D5D8DC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -387,6 +466,53 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -775,6 +901,757 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="46" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>开发阶段规划 — 先做什么后做什么，每步目的是什么、能实现什么</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="54" t="inlineStr">
+        <is>
+          <t>按依赖关系排出8个阶段，必须从P1到P8顺序做（后面的依赖前面的）。每个阶段做完都有"能跑起来看到的东西"，不是做完一堆代码什么反应都没有。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="24" t="inlineStr"/>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>阶段</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>阶段名称</t>
+        </is>
+      </c>
+      <c r="D3" s="24" t="inlineStr">
+        <is>
+          <t>做什么（内容）</t>
+        </is>
+      </c>
+      <c r="E3" s="24" t="inlineStr">
+        <is>
+          <t>目的（为什么先做这个）</t>
+        </is>
+      </c>
+      <c r="F3" s="24" t="inlineStr">
+        <is>
+          <t>能实现的进展（做完能看到什么）</t>
+        </is>
+      </c>
+      <c r="G3" s="24" t="inlineStr">
+        <is>
+          <t>验证标准（怎么算做完）</t>
+        </is>
+      </c>
+      <c r="H3" s="24" t="inlineStr">
+        <is>
+          <t>对应主表编号</t>
+        </is>
+      </c>
+      <c r="I3" s="24" t="inlineStr">
+        <is>
+          <t>周期</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="120" customHeight="1">
+      <c r="B4" s="58" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C4" s="58" t="inlineStr">
+        <is>
+          <t>引擎骨架</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>渲染循环(Director)
+输入系统(Input)
+事件总线(EventSystem)
+场景管理(SceneManager)
+渲染器(Renderer)</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>这是整个游戏的地基。没有渲染循环什么也跑不起来，没有输入系统什么也点不了。必须先搭好引擎框架，后面所有功能才能挂上去。</t>
+        </is>
+      </c>
+      <c r="F4" s="59" t="inlineStr">
+        <is>
+          <t>能看到一个黑色画布在60fps跑
+能在画布上画矩形/文字
+点屏幕能触发回调
+能切换空场景A和空场景B</t>
+        </is>
+      </c>
+      <c r="G4" s="39" t="inlineStr">
+        <is>
+          <t>①Director.loop 60fps跑通
+②点击屏幕console打印坐标
+③画矩形和文字能显示
+④场景A能切换到场景B</t>
+        </is>
+      </c>
+      <c r="H4" s="60" t="inlineStr">
+        <is>
+          <t>A1.01~A1.04
+A2.01~A2.04
+A3.01~A3.03
+A4.01~A4.02
+A5.01~A5.03</t>
+        </is>
+      </c>
+      <c r="I4" s="61" t="inlineStr">
+        <is>
+          <t>1周</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="120" customHeight="1">
+      <c r="B5" s="62" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C5" s="62" t="inlineStr">
+        <is>
+          <t>数据层</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>常量配置(Constants)
+卡牌数据表(Cards)
+卡组手牌(Deck)
+预设卡组(DeckPresets)</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>引擎能跑了，但游戏需要数据。卡牌属性、灵力参数、棋盘尺寸等所有数值必须先配置好，后面的战斗逻辑才能读数据创建单位。配置驱动是核心原则——改数值只改配置不改代码。</t>
+        </is>
+      </c>
+      <c r="F5" s="59" t="inlineStr">
+        <is>
+          <t>19张卡牌数据完整可查
+8张卡组能洗牌+抽牌
+能console打印手牌和卡牌属性
+改Cards.js数值能立即生效</t>
+        </is>
+      </c>
+      <c r="G5" s="39" t="inlineStr">
+        <is>
+          <t>①Cards.get(id)返回完整属性
+②Deck.init后hand有3张牌
+③Deck.draw能抽牌
+④canPlay能正确判断灵力</t>
+        </is>
+      </c>
+      <c r="H5" s="60" t="inlineStr">
+        <is>
+          <t>B1.01
+B2.01~B2.02
+B3.01~B3.06
+B4.01</t>
+        </is>
+      </c>
+      <c r="I5" s="61" t="inlineStr">
+        <is>
+          <t>1周</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="120" customHeight="1">
+      <c r="B6" s="63" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C6" s="63" t="inlineStr">
+        <is>
+          <t>核心战斗逻辑</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>战斗主循环(BattleLogic)
+单位实体(Unit)
+移动系统(Movement)
+战斗系统(Combat)
+★击杀后继续推进★</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>这是整个游戏好不好玩的命门。单位能不能走、能不能打、打完能不能继续冲——这3件事决定了游戏核心循环是否成立。必须在这个阶段验证"攻方打得动"。</t>
+        </is>
+      </c>
+      <c r="F6" s="59" t="inlineStr">
+        <is>
+          <t>★最重要的里程碑★
+AI vs AI模拟能跑通
+能看到单位在棋盘上移动
+能看到单位互相打
+能看到单位杀掉敌人后继续冲
+能看到单位到大殿造成伤害</t>
+        </is>
+      </c>
+      <c r="G6" s="39" t="inlineStr">
+        <is>
+          <t>①单位y坐标每帧变化(在走)
+②两个单位接触后互扣血
+③单位击杀后state=walking继续走
+④单位到大殿后大殿血量减少</t>
+        </is>
+      </c>
+      <c r="H6" s="60" t="inlineStr">
+        <is>
+          <t>C1.01
+C2.01~C2.04
+C3.01~C3.04
+C4.01~C4.06</t>
+        </is>
+      </c>
+      <c r="I6" s="61" t="inlineStr">
+        <is>
+          <t>2周</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="120" customHeight="1">
+      <c r="B7" s="64" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="C7" s="64" t="inlineStr">
+        <is>
+          <t>扩展战斗机制</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>阵法系统(布阵/攻击/冷却)
+法术系统(8种法术效果)
+长老技能(4分支随机)
+灵力系统(实时回复)
+出牌执行
+胜负判定
+死亡清理</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>核心循环跑通了，但只有"走和打"太单调。阵法让守方能防，法术增加策略深度，长老增加变化性，灵力系统驱动出牌节奏。这些让游戏从"能跑"变成"好玩"。</t>
+        </is>
+      </c>
+      <c r="F7" s="59" t="inlineStr">
+        <is>
+          <t>完整单局能跑通
+能布阵拦截(阵法有血量会攻击)
+能放法术(8种效果各不相同)
+长老每5秒随机放技能
+灵力实时回复能出牌
+能判定胜负(大殿破/超时)</t>
+        </is>
+      </c>
+      <c r="G7" s="39" t="inlineStr">
+        <is>
+          <t>①布阵后阵法能攻击经过敌人
+②阵法被毁后格子8秒冷却
+③8种法术效果各自正确生效
+④长老每5秒释放1个随机分支
+⑤灵力每2.8秒+1
+⑥大殿血量归零能判定胜负</t>
+        </is>
+      </c>
+      <c r="H7" s="60" t="inlineStr">
+        <is>
+          <t>C5.01~C5.04
+C6.01~C6.09
+C7.01~C7.06
+C8.01~C8.02
+C9.01~C9.02
+C10.01~C10.03
+C11.01~C11.02</t>
+        </is>
+      </c>
+      <c r="I7" s="61" t="inlineStr">
+        <is>
+          <t>2周</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="120" customHeight="1">
+      <c r="B8" s="65" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="C8" s="65" t="inlineStr">
+        <is>
+          <t>AI对手</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>AI决策(灵力管理/出牌/布阵)
+3档难度(简单/普通/困难)</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>战斗逻辑完整了，但需要对手。没有AI玩家无法测试游戏好不好玩。AI不需要完美，但要能模拟真人节奏出牌布阵，让你能完整体验一局对战。</t>
+        </is>
+      </c>
+      <c r="F8" s="59" t="inlineStr">
+        <is>
+          <t>能和AI完整打一局(纯逻辑)
+AI会出兵也会布阵
+AI会根据血量调整攻守
+简单AI弱/困难AI强有明显差异</t>
+        </is>
+      </c>
+      <c r="G8" s="39" t="inlineStr">
+        <is>
+          <t>①AI每2.5秒(普通)决策一次
+②AI会根据大殿血量调攻守比
+③简单/普通/困难行为有差异
+④AI vs AI能完整跑完一局不卡死</t>
+        </is>
+      </c>
+      <c r="H8" s="60" t="inlineStr">
+        <is>
+          <t>D1.01~D1.05
+D2.01~D2.03</t>
+        </is>
+      </c>
+      <c r="I8" s="61" t="inlineStr">
+        <is>
+          <t>1周</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="120" customHeight="1">
+      <c r="B9" s="66" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="C9" s="66" t="inlineStr">
+        <is>
+          <t>渲染与交互</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>战斗场景(分层渲染)
+背景/大殿/单位/阵法渲染
+手牌栏/灵力条/HUD
+出牌交互(选牌→选目标)
+结算场景
+新手引导
+粒子特效
+音频</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>到这一步为止游戏都是"纯逻辑"——console里跑数字。P6把所有逻辑变成"能看到能操作的画面"。这是从"程序员眼里的游戏"变成"玩家眼里的游戏"的关键。</t>
+        </is>
+      </c>
+      <c r="F9" s="59" t="inlineStr">
+        <is>
+          <t>★玩家可见里程碑★
+能在微信开发者工具里看到画面
+能看到棋盘/大殿/单位/阵法
+能点手牌出牌、点格子布阵
+能看到灵力条/血条/计时器
+战斗结束有结算页
+新手引导能走通4步</t>
+        </is>
+      </c>
+      <c r="G9" s="39" t="inlineStr">
+        <is>
+          <t>①真机/开发者工具能显示画面
+②点手牌→选目标→出牌流程通
+③单位移动/交战有视觉反馈
+④大殿受击有震动+闪烁
+⑤结算页显示胜负+摧毁度
+⑥新手引导4步走通</t>
+        </is>
+      </c>
+      <c r="H9" s="60" t="inlineStr">
+        <is>
+          <t>E1.01~E1.04
+E2.01~E2.02
+E3.01~E3.03
+E4.01~E4.03
+E5.01~E5.02
+E6.01~E6.03
+E7.01
+E8.01~E8.02
+E9.01~E9.02
+E10.01~E10.03
+E11.01~E11.04</t>
+        </is>
+      </c>
+      <c r="I9" s="61" t="inlineStr">
+        <is>
+          <t>2周</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="120" customHeight="1">
+      <c r="B10" s="67" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="C10" s="67" t="inlineStr">
+        <is>
+          <t>测试与平衡调优</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>纯逻辑模拟器(AI vs AI 10局)
+平衡性调优(参数调整)
+性能测试(60fps/内存)
+真机测试
+Bug修复</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>游戏能玩了，但好不好玩是另一回事。P7用模拟器跑大量对局验证平衡——攻方能不能打进去、守方能不能防下来、有没有0%死局。调到"双方都有来有回"才算过关。</t>
+        </is>
+      </c>
+      <c r="F10" s="59" t="inlineStr">
+        <is>
+          <t>★平衡达标里程碑★
+模拟10局输出摧毁度/胜率数据
+参数调到双方摧毁度20~70%
+真机60fps不卡
+无崩溃无死锁</t>
+        </is>
+      </c>
+      <c r="G10" s="39" t="inlineStr">
+        <is>
+          <t>①模拟10局: 摧毁度20~70%
+②胜率40~60%
+③0%摧毁度对局&lt;10%
+④90%对局150~210秒结束
+⑤真机60fps同屏20单位不卡</t>
+        </is>
+      </c>
+      <c r="H10" s="60" t="inlineStr">
+        <is>
+          <t>全部联调
+(卡牌数据/数值配置)</t>
+        </is>
+      </c>
+      <c r="I10" s="61" t="inlineStr">
+        <is>
+          <t>1.5周</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="120" customHeight="1">
+      <c r="B11" s="68" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="C11" s="68" t="inlineStr">
+        <is>
+          <t>提交审核上线</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>最终Bug修复
+微信小游戏审核提交
+审核反馈处理
+正式上线</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>游戏做完要上线才能让玩家玩到。微信小游戏需要提交审核，修仙题材过审风险低但仍需确保无违规内容。这是V1的终点。</t>
+        </is>
+      </c>
+      <c r="F11" s="59" t="inlineStr">
+        <is>
+          <t>★V1上线里程碑★
+微信审核通过
+玩家能搜索到并玩到游戏
+V1 MVP完成</t>
+        </is>
+      </c>
+      <c r="G11" s="39" t="inlineStr">
+        <is>
+          <t>①微信审核通过
+②玩家能正常游玩
+③无严重Bug
+④新手引导完成率&gt;80%</t>
+        </is>
+      </c>
+      <c r="H11" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I11" s="61" t="inlineStr">
+        <is>
+          <t>1周</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="B13" s="69" t="inlineStr">
+        <is>
+          <t>P1引擎骨架 → P2数据层 → P3核心战斗 → P4扩展战斗 → P5 AI对手 → P6渲染交互 → P7测试平衡 → P8上线   （必须按顺序，后面依赖前面）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>关键里程碑（做完能看到的东西）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="B16" s="70" t="inlineStr">
+        <is>
+          <t>P1做完</t>
+        </is>
+      </c>
+      <c r="C16" s="55" t="inlineStr">
+        <is>
+          <t>黑色画布在跑，能画能点</t>
+        </is>
+      </c>
+      <c r="H16" s="71" t="inlineStr">
+        <is>
+          <t>代码能跑</t>
+        </is>
+      </c>
+      <c r="I16" s="72" t="n"/>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="B17" s="70" t="inlineStr">
+        <is>
+          <t>P3做完</t>
+        </is>
+      </c>
+      <c r="C17" s="55" t="inlineStr">
+        <is>
+          <t>★最重要★ AI vs AI模拟能看到单位走、打、突破</t>
+        </is>
+      </c>
+      <c r="H17" s="71" t="inlineStr">
+        <is>
+          <t>核心循环成立</t>
+        </is>
+      </c>
+      <c r="I17" s="72" t="n"/>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="B18" s="70" t="inlineStr">
+        <is>
+          <t>P5做完</t>
+        </is>
+      </c>
+      <c r="C18" s="55" t="inlineStr">
+        <is>
+          <t>纯逻辑能和AI打一局完整对战</t>
+        </is>
+      </c>
+      <c r="H18" s="71" t="inlineStr">
+        <is>
+          <t>逻辑层完成</t>
+        </is>
+      </c>
+      <c r="I18" s="72" t="n"/>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="B19" s="70" t="inlineStr">
+        <is>
+          <t>P6做完</t>
+        </is>
+      </c>
+      <c r="C19" s="55" t="inlineStr">
+        <is>
+          <t>★玩家可见★ 微信工具里能看到画面能操作</t>
+        </is>
+      </c>
+      <c r="H19" s="71" t="inlineStr">
+        <is>
+          <t>能玩了</t>
+        </is>
+      </c>
+      <c r="I19" s="72" t="n"/>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="B20" s="70" t="inlineStr">
+        <is>
+          <t>P7做完</t>
+        </is>
+      </c>
+      <c r="C20" s="55" t="inlineStr">
+        <is>
+          <t>★平衡达标★ 模拟10局双方都能打出伤害</t>
+        </is>
+      </c>
+      <c r="H20" s="71" t="inlineStr">
+        <is>
+          <t>好玩了</t>
+        </is>
+      </c>
+      <c r="I20" s="72" t="n"/>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="B21" s="70" t="inlineStr">
+        <is>
+          <t>P8做完</t>
+        </is>
+      </c>
+      <c r="C21" s="55" t="inlineStr">
+        <is>
+          <t>★V1上线★ 微信审核通过玩家能玩</t>
+        </is>
+      </c>
+      <c r="H21" s="71" t="inlineStr">
+        <is>
+          <t>V1完成</t>
+        </is>
+      </c>
+      <c r="I21" s="72" t="n"/>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="B24" s="73" t="inlineStr">
+        <is>
+          <t>每日开发指引（照着做就行）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="B25" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  第1步：看本表，确认当前在哪个阶段（比如P3）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="B26" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  第2步：打开「2.开发主表」，找到当前阶段对应的编号（如C3.01）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="B27" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  第3步：看那一行的"L4实现原理"和"L5函数"——那就是要做的</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="B28" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  第4步：用「AI提问指南」的模板，把原理+函数名发给AI让它实现</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="B29" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  第5步：AI做完后，按本阶段的"验证标准"自己验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="B30" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  第6步：验证通过→主表状态改"已完成"→做下一个</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="B31" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  第7步：当前阶段所有功能都做完→进入下一阶段</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="B32" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  原则：一个阶段做完再进下一个，不要跳着做。每阶段都有里程碑，做完能看到东西。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="25">
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="B25:I25"/>
+    <mergeCell ref="B31:I31"/>
+    <mergeCell ref="B27:I27"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="B13:I13"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="B29:I29"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="B28:I28"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="B30:I30"/>
+    <mergeCell ref="B15:I15"/>
+    <mergeCell ref="B24:I24"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="B32:I32"/>
+    <mergeCell ref="B26:I26"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -813,6 +1690,9 @@
           <t>宗门论道（暂定）</t>
         </is>
       </c>
+      <c r="D4" s="74" t="n"/>
+      <c r="E4" s="74" t="n"/>
+      <c r="F4" s="72" t="n"/>
     </row>
     <row r="5" ht="28" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
@@ -825,6 +1705,9 @@
           <t>实时策略卡牌（RTS-lite + 卡牌费用制）</t>
         </is>
       </c>
+      <c r="D5" s="74" t="n"/>
+      <c r="E5" s="74" t="n"/>
+      <c r="F5" s="72" t="n"/>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="B6" s="3" t="inlineStr">
@@ -837,6 +1720,9 @@
           <t>东方修仙 / 宗门大战</t>
         </is>
       </c>
+      <c r="D6" s="74" t="n"/>
+      <c r="E6" s="74" t="n"/>
+      <c r="F6" s="72" t="n"/>
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="B7" s="3" t="inlineStr">
@@ -849,6 +1735,9 @@
           <t>微信小游戏（Canvas 2D 渲染）</t>
         </is>
       </c>
+      <c r="D7" s="74" t="n"/>
+      <c r="E7" s="74" t="n"/>
+      <c r="F7" s="72" t="n"/>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="B8" s="3" t="inlineStr">
@@ -861,6 +1750,9 @@
           <t>3~5 分钟（180秒正赛 + 60秒加时）</t>
         </is>
       </c>
+      <c r="D8" s="74" t="n"/>
+      <c r="E8" s="74" t="n"/>
+      <c r="F8" s="72" t="n"/>
     </row>
     <row r="9" ht="28" customHeight="1">
       <c r="B9" s="3" t="inlineStr">
@@ -873,6 +1765,9 @@
           <t>18~35岁，喜欢轻度策略、修仙题材、碎片化对战的玩家</t>
         </is>
       </c>
+      <c r="D9" s="74" t="n"/>
+      <c r="E9" s="74" t="n"/>
+      <c r="F9" s="72" t="n"/>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="B10" s="3" t="inlineStr">
@@ -885,6 +1780,9 @@
           <t>皇室战争式的实时卡牌攻防，修仙皮——你与对手各据山门一座，实时派弟子出征、布阵拦截、长老施法，摧毁对方宗门大殿者胜。</t>
         </is>
       </c>
+      <c r="D10" s="74" t="n"/>
+      <c r="E10" s="74" t="n"/>
+      <c r="F10" s="72" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
@@ -899,9 +1797,17 @@
           <t>你和对手各据一座宗门大殿（30血），实时同时出兵互攻，谁先拆掉对方大殿谁赢，3分钟时限。</t>
         </is>
       </c>
+      <c r="C13" s="74" t="n"/>
+      <c r="D13" s="74" t="n"/>
+      <c r="E13" s="74" t="n"/>
+      <c r="F13" s="72" t="n"/>
     </row>
     <row r="14" ht="8" customHeight="1">
       <c r="B14" s="4" t="inlineStr"/>
+      <c r="C14" s="74" t="n"/>
+      <c r="D14" s="74" t="n"/>
+      <c r="E14" s="74" t="n"/>
+      <c r="F14" s="72" t="n"/>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="B15" s="6" t="inlineStr">
@@ -909,6 +1815,10 @@
           <t>【你做什么】</t>
         </is>
       </c>
+      <c r="C15" s="74" t="n"/>
+      <c r="D15" s="74" t="n"/>
+      <c r="E15" s="74" t="n"/>
+      <c r="F15" s="72" t="n"/>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="B16" s="4" t="inlineStr">
@@ -916,6 +1826,10 @@
           <t xml:space="preserve">  1. 出兵：花灵力出弟子（体修/剑修/御兽），单位自动沿山道向敌方大殿推进，遇敌自动交战，杀完继续冲</t>
         </is>
       </c>
+      <c r="C16" s="74" t="n"/>
+      <c r="D16" s="74" t="n"/>
+      <c r="E16" s="74" t="n"/>
+      <c r="F16" s="72" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1">
       <c r="B17" s="4" t="inlineStr">
@@ -923,6 +1837,10 @@
           <t xml:space="preserve">  2. 布阵：在主路两侧阵法区布阵法（不动，拦截+攻击经过的敌人），剑阵双方通用</t>
         </is>
       </c>
+      <c r="C17" s="74" t="n"/>
+      <c r="D17" s="74" t="n"/>
+      <c r="E17" s="74" t="n"/>
+      <c r="F17" s="72" t="n"/>
     </row>
     <row r="18" ht="24" customHeight="1">
       <c r="B18" s="4" t="inlineStr">
@@ -930,6 +1848,10 @@
           <t xml:space="preserve">  3. 施法：放法术（五雷正法范围炸、万剑归宗全队加速、金钟罩大殿免疫等）</t>
         </is>
       </c>
+      <c r="C18" s="74" t="n"/>
+      <c r="D18" s="74" t="n"/>
+      <c r="E18" s="74" t="n"/>
+      <c r="F18" s="72" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
       <c r="B19" s="4" t="inlineStr">
@@ -937,9 +1859,17 @@
           <t xml:space="preserve">  4. 出长老：花6费出金丹长老，每5秒随机释放飞剑/丹药/符箓/御兽分支技能</t>
         </is>
       </c>
+      <c r="C19" s="74" t="n"/>
+      <c r="D19" s="74" t="n"/>
+      <c r="E19" s="74" t="n"/>
+      <c r="F19" s="72" t="n"/>
     </row>
     <row r="20" ht="8" customHeight="1">
       <c r="B20" s="4" t="inlineStr"/>
+      <c r="C20" s="74" t="n"/>
+      <c r="D20" s="74" t="n"/>
+      <c r="E20" s="74" t="n"/>
+      <c r="F20" s="72" t="n"/>
     </row>
     <row r="21" ht="24" customHeight="1">
       <c r="B21" s="6" t="inlineStr">
@@ -947,6 +1877,10 @@
           <t>【灵力系统】</t>
         </is>
       </c>
+      <c r="C21" s="74" t="n"/>
+      <c r="D21" s="74" t="n"/>
+      <c r="E21" s="74" t="n"/>
+      <c r="F21" s="72" t="n"/>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="B22" s="4" t="inlineStr">
@@ -954,9 +1888,17 @@
           <t xml:space="preserve">  实时回复：每2.8秒+1，开局上限5随时间涨到10。灵力不够出不了牌——攒大单位还是铺小单位，是核心决策。</t>
         </is>
       </c>
+      <c r="C22" s="74" t="n"/>
+      <c r="D22" s="74" t="n"/>
+      <c r="E22" s="74" t="n"/>
+      <c r="F22" s="72" t="n"/>
     </row>
     <row r="23" ht="8" customHeight="1">
       <c r="B23" s="4" t="inlineStr"/>
+      <c r="C23" s="74" t="n"/>
+      <c r="D23" s="74" t="n"/>
+      <c r="E23" s="74" t="n"/>
+      <c r="F23" s="72" t="n"/>
     </row>
     <row r="24" ht="24" customHeight="1">
       <c r="B24" s="6" t="inlineStr">
@@ -964,6 +1906,10 @@
           <t>【地图视角】折中方案：逻辑上下直推 + 视觉山道攻山 + 两侧阵法区</t>
         </is>
       </c>
+      <c r="C24" s="74" t="n"/>
+      <c r="D24" s="74" t="n"/>
+      <c r="E24" s="74" t="n"/>
+      <c r="F24" s="72" t="n"/>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
@@ -978,6 +1924,10 @@
           <t xml:space="preserve">     ┌─────────────────────────┐</t>
         </is>
       </c>
+      <c r="C27" s="74" t="n"/>
+      <c r="D27" s="74" t="n"/>
+      <c r="E27" s="74" t="n"/>
+      <c r="F27" s="72" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="B28" s="8" t="inlineStr">
@@ -985,6 +1935,10 @@
           <t xml:space="preserve">     │      [敌方大殿] 30血     │  ← 你要拆的（顶端）</t>
         </is>
       </c>
+      <c r="C28" s="74" t="n"/>
+      <c r="D28" s="74" t="n"/>
+      <c r="E28" s="74" t="n"/>
+      <c r="F28" s="72" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="B29" s="8" t="inlineStr">
@@ -992,6 +1946,10 @@
           <t xml:space="preserve">     │  阵法区│主路│阵法区      │  ← 两侧可布阵拦截</t>
         </is>
       </c>
+      <c r="C29" s="74" t="n"/>
+      <c r="D29" s="74" t="n"/>
+      <c r="E29" s="74" t="n"/>
+      <c r="F29" s="72" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="B30" s="8" t="inlineStr">
@@ -999,6 +1957,10 @@
           <t xml:space="preserve">     │       │    │            │</t>
         </is>
       </c>
+      <c r="C30" s="74" t="n"/>
+      <c r="D30" s="74" t="n"/>
+      <c r="E30" s="74" t="n"/>
+      <c r="F30" s="72" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="B31" s="8" t="inlineStr">
@@ -1006,6 +1968,10 @@
           <t xml:space="preserve">     │  阵法区│主路│阵法区      │  ← 中段，单位在此交战</t>
         </is>
       </c>
+      <c r="C31" s="74" t="n"/>
+      <c r="D31" s="74" t="n"/>
+      <c r="E31" s="74" t="n"/>
+      <c r="F31" s="72" t="n"/>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="B32" s="8" t="inlineStr">
@@ -1013,6 +1979,10 @@
           <t xml:space="preserve">     │       │    │            │</t>
         </is>
       </c>
+      <c r="C32" s="74" t="n"/>
+      <c r="D32" s="74" t="n"/>
+      <c r="E32" s="74" t="n"/>
+      <c r="F32" s="72" t="n"/>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="B33" s="8" t="inlineStr">
@@ -1020,6 +1990,10 @@
           <t xml:space="preserve">     │  阵法区│主路│阵法区      │  ← 下段</t>
         </is>
       </c>
+      <c r="C33" s="74" t="n"/>
+      <c r="D33" s="74" t="n"/>
+      <c r="E33" s="74" t="n"/>
+      <c r="F33" s="72" t="n"/>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="B34" s="8" t="inlineStr">
@@ -1027,6 +2001,10 @@
           <t xml:space="preserve">     │      [我方大殿] 30血     │  ← 你要守的（底端）</t>
         </is>
       </c>
+      <c r="C34" s="74" t="n"/>
+      <c r="D34" s="74" t="n"/>
+      <c r="E34" s="74" t="n"/>
+      <c r="F34" s="72" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="B35" s="8" t="inlineStr">
@@ -1034,6 +2012,10 @@
           <t xml:space="preserve">     └─────────────────────────┘</t>
         </is>
       </c>
+      <c r="C35" s="74" t="n"/>
+      <c r="D35" s="74" t="n"/>
+      <c r="E35" s="74" t="n"/>
+      <c r="F35" s="72" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="B36" s="8" t="inlineStr">
@@ -1041,6 +2023,10 @@
           <t xml:space="preserve">     单位沿主路向上推进（2朝向：上/下），背景做成山道攻山感</t>
         </is>
       </c>
+      <c r="C36" s="74" t="n"/>
+      <c r="D36" s="74" t="n"/>
+      <c r="E36" s="74" t="n"/>
+      <c r="F36" s="72" t="n"/>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="9" t="inlineStr">
@@ -1060,6 +2046,9 @@
           <t>为什么做实时不做回合制？</t>
         </is>
       </c>
+      <c r="D39" s="74" t="n"/>
+      <c r="E39" s="74" t="n"/>
+      <c r="F39" s="72" t="n"/>
     </row>
     <row r="40" ht="50" customHeight="1">
       <c r="B40" s="12" t="inlineStr">
@@ -1072,6 +2061,9 @@
           <t>回合制的痛点：等对方出招很无聊，节奏慢。实时制双方同时操作互不等待，每一秒都有决策压力，紧张感是核心体验。参考皇室战争成功验证了这一点。</t>
         </is>
       </c>
+      <c r="D40" s="74" t="n"/>
+      <c r="E40" s="74" t="n"/>
+      <c r="F40" s="72" t="n"/>
     </row>
     <row r="41" ht="26" customHeight="1">
       <c r="B41" s="10" t="inlineStr">
@@ -1084,6 +2076,9 @@
           <t>为什么攻方"击杀后继续推进"？</t>
         </is>
       </c>
+      <c r="D41" s="74" t="n"/>
+      <c r="E41" s="74" t="n"/>
+      <c r="F41" s="72" t="n"/>
     </row>
     <row r="42" ht="50" customHeight="1">
       <c r="B42" s="12" t="inlineStr">
@@ -1096,6 +2091,9 @@
           <t>★这是最核心的设计修复★。旧版"遇阵即停打完即没"导致攻方永远过不去，0%摧毁度。改成击杀后不消失继续冲，攻方才有突破感，守方才有"阵被破"的危机感。这是整个游戏好不好玩的命门。</t>
         </is>
       </c>
+      <c r="D42" s="74" t="n"/>
+      <c r="E42" s="74" t="n"/>
+      <c r="F42" s="72" t="n"/>
     </row>
     <row r="43" ht="26" customHeight="1">
       <c r="B43" s="10" t="inlineStr">
@@ -1108,6 +2106,9 @@
           <t>为什么阵法有8秒冷却？</t>
         </is>
       </c>
+      <c r="D43" s="74" t="n"/>
+      <c r="E43" s="74" t="n"/>
+      <c r="F43" s="72" t="n"/>
     </row>
     <row r="44" ht="50" customHeight="1">
       <c r="B44" s="12" t="inlineStr">
@@ -1120,6 +2121,9 @@
           <t>防止守方无限补阵堵路。阵被破后该格8秒不能再布，攻方有突破窗口。这创造了"攻守博弈"的节奏：守方要判断哪格该补、哪格该放弃。</t>
         </is>
       </c>
+      <c r="D44" s="74" t="n"/>
+      <c r="E44" s="74" t="n"/>
+      <c r="F44" s="72" t="n"/>
     </row>
     <row r="45" ht="26" customHeight="1">
       <c r="B45" s="10" t="inlineStr">
@@ -1132,6 +2136,9 @@
           <t>为什么用折中视角不用斜45度？</t>
         </is>
       </c>
+      <c r="D45" s="74" t="n"/>
+      <c r="E45" s="74" t="n"/>
+      <c r="F45" s="72" t="n"/>
     </row>
     <row r="46" ht="50" customHeight="1">
       <c r="B46" s="12" t="inlineStr">
@@ -1144,6 +2151,9 @@
           <t>纯斜45度等距视角美术成本3~4倍（每单位需8方向vs2方向），碰撞复杂（菱形vs矩形）。折中方案：逻辑上下直推（实现简单），视觉做成山道攻山（保留修仙味），两全其美。</t>
         </is>
       </c>
+      <c r="D46" s="74" t="n"/>
+      <c r="E46" s="74" t="n"/>
+      <c r="F46" s="72" t="n"/>
     </row>
     <row r="47" ht="26" customHeight="1">
       <c r="B47" s="10" t="inlineStr">
@@ -1156,6 +2166,9 @@
           <t>为什么金丹长老是随机技能？</t>
         </is>
       </c>
+      <c r="D47" s="74" t="n"/>
+      <c r="E47" s="74" t="n"/>
+      <c r="F47" s="72" t="n"/>
     </row>
     <row r="48" ht="50" customHeight="1">
       <c r="B48" s="12" t="inlineStr">
@@ -1168,6 +2181,9 @@
           <t>固定技能会变成"最优解"——玩家算出哪个分支最强就只用那个。随机性增加不可预测性，每次出长老都有惊喜/惊吓，增加对局变化和观赏性。</t>
         </is>
       </c>
+      <c r="D48" s="74" t="n"/>
+      <c r="E48" s="74" t="n"/>
+      <c r="F48" s="72" t="n"/>
     </row>
     <row r="49" ht="26" customHeight="1">
       <c r="B49" s="10" t="inlineStr">
@@ -1180,6 +2196,9 @@
           <t>为什么剑阵双方通用？</t>
         </is>
       </c>
+      <c r="D49" s="74" t="n"/>
+      <c r="E49" s="74" t="n"/>
+      <c r="F49" s="72" t="n"/>
     </row>
     <row r="50" ht="50" customHeight="1">
       <c r="B50" s="12" t="inlineStr">
@@ -1192,6 +2211,9 @@
           <t>如果阵法只能防守用，攻方缺乏掩护手段。双方通用后，攻方可铺阵掩护推进（阵法跟着部队走），守方布阵拦截，策略空间更大。</t>
         </is>
       </c>
+      <c r="D50" s="74" t="n"/>
+      <c r="E50" s="74" t="n"/>
+      <c r="F50" s="72" t="n"/>
     </row>
     <row r="51" ht="26" customHeight="1">
       <c r="B51" s="10" t="inlineStr">
@@ -1204,6 +2226,9 @@
           <t>为什么选修仙题材？</t>
         </is>
       </c>
+      <c r="D51" s="74" t="n"/>
+      <c r="E51" s="74" t="n"/>
+      <c r="F51" s="72" t="n"/>
     </row>
     <row r="52" ht="50" customHeight="1">
       <c r="B52" s="12" t="inlineStr">
@@ -1216,6 +2241,9 @@
           <t>①国内过审零风险（法术不血腥）②修仙认知度高（飞剑/阵法/灵兽玩家秒懂）③"攻山"主题与推塔玩法天然契合④市场有验证（一念逍遥等）。现代战争过审风险极高，科幻需重设题材。</t>
         </is>
       </c>
+      <c r="D52" s="74" t="n"/>
+      <c r="E52" s="74" t="n"/>
+      <c r="F52" s="72" t="n"/>
     </row>
     <row r="53" ht="26" customHeight="1">
       <c r="B53" s="10" t="inlineStr">
@@ -1228,6 +2256,9 @@
           <t>为什么V1先做3个流派？</t>
         </is>
       </c>
+      <c r="D53" s="74" t="n"/>
+      <c r="E53" s="74" t="n"/>
+      <c r="F53" s="72" t="n"/>
     </row>
     <row r="54" ht="50" customHeight="1">
       <c r="B54" s="12" t="inlineStr">
@@ -1240,6 +2271,9 @@
           <t>MVP原则：用最少的验证核心玩法。剑修（突进）+符修（远程）+阵修（防守）覆盖了攻防基本循环。验证好玩后再加丹修/傀儡/御兽，避免过度设计。</t>
         </is>
       </c>
+      <c r="D54" s="74" t="n"/>
+      <c r="E54" s="74" t="n"/>
+      <c r="F54" s="72" t="n"/>
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="14" t="inlineStr">
@@ -1254,6 +2288,10 @@
           <t>攻方保障（能攻进去）</t>
         </is>
       </c>
+      <c r="C57" s="74" t="n"/>
+      <c r="D57" s="74" t="n"/>
+      <c r="E57" s="74" t="n"/>
+      <c r="F57" s="72" t="n"/>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="B58" s="4" t="inlineStr">
@@ -1261,6 +2299,10 @@
           <t xml:space="preserve">  1. 单位击杀后继续推进（不消失）——攻方有突破感</t>
         </is>
       </c>
+      <c r="C58" s="74" t="n"/>
+      <c r="D58" s="74" t="n"/>
+      <c r="E58" s="74" t="n"/>
+      <c r="F58" s="72" t="n"/>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="B59" s="4" t="inlineStr">
@@ -1268,6 +2310,10 @@
           <t xml:space="preserve">  2. 阵法被毁格子8秒冷却——守方不能无限堵路</t>
         </is>
       </c>
+      <c r="C59" s="74" t="n"/>
+      <c r="D59" s="74" t="n"/>
+      <c r="E59" s="74" t="n"/>
+      <c r="F59" s="72" t="n"/>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="B60" s="4" t="inlineStr">
@@ -1275,6 +2321,10 @@
           <t xml:space="preserve">  3. 攻方有破阵工具：体修扛伤、五雷正法清阵、爆裂符换阵</t>
         </is>
       </c>
+      <c r="C60" s="74" t="n"/>
+      <c r="D60" s="74" t="n"/>
+      <c r="E60" s="74" t="n"/>
+      <c r="F60" s="72" t="n"/>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="B61" s="4" t="inlineStr">
@@ -1282,6 +2332,10 @@
           <t xml:space="preserve">  4. 灵力实时回复——攻方可持续出兵施压</t>
         </is>
       </c>
+      <c r="C61" s="74" t="n"/>
+      <c r="D61" s="74" t="n"/>
+      <c r="E61" s="74" t="n"/>
+      <c r="F61" s="72" t="n"/>
     </row>
     <row r="63" ht="28" customHeight="1">
       <c r="B63" s="16" t="inlineStr">
@@ -1289,6 +2343,10 @@
           <t>守方保障（能防下来）</t>
         </is>
       </c>
+      <c r="C63" s="74" t="n"/>
+      <c r="D63" s="74" t="n"/>
+      <c r="E63" s="74" t="n"/>
+      <c r="F63" s="72" t="n"/>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="B64" s="4" t="inlineStr">
@@ -1296,6 +2354,10 @@
           <t xml:space="preserve">  1. 阵法便宜性价比高（截脉阵费2血4，换攻方更多时间）</t>
         </is>
       </c>
+      <c r="C64" s="74" t="n"/>
+      <c r="D64" s="74" t="n"/>
+      <c r="E64" s="74" t="n"/>
+      <c r="F64" s="72" t="n"/>
     </row>
     <row r="65" ht="22" customHeight="1">
       <c r="B65" s="4" t="inlineStr">
@@ -1303,6 +2365,10 @@
           <t xml:space="preserve">  2. 多阵叠加+特种阵法：寒霜减速、反震反伤、天罗范围</t>
         </is>
       </c>
+      <c r="C65" s="74" t="n"/>
+      <c r="D65" s="74" t="n"/>
+      <c r="E65" s="74" t="n"/>
+      <c r="F65" s="72" t="n"/>
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="B66" s="4" t="inlineStr">
@@ -1310,6 +2376,10 @@
           <t xml:space="preserve">  3. 反制法术兜底：金钟罩免疫、移山倒海推后、困仙索定身</t>
         </is>
       </c>
+      <c r="C66" s="74" t="n"/>
+      <c r="D66" s="74" t="n"/>
+      <c r="E66" s="74" t="n"/>
+      <c r="F66" s="72" t="n"/>
     </row>
     <row r="67" ht="22" customHeight="1">
       <c r="B67" s="4" t="inlineStr">
@@ -1317,6 +2387,10 @@
           <t xml:space="preserve">  4. 护山傀儡/灵兽提供肉盾拦截</t>
         </is>
       </c>
+      <c r="C67" s="74" t="n"/>
+      <c r="D67" s="74" t="n"/>
+      <c r="E67" s="74" t="n"/>
+      <c r="F67" s="72" t="n"/>
     </row>
     <row r="69" ht="28" customHeight="1">
       <c r="B69" s="17" t="inlineStr">
@@ -1324,6 +2398,10 @@
           <t>平衡验证标准</t>
         </is>
       </c>
+      <c r="C69" s="74" t="n"/>
+      <c r="D69" s="74" t="n"/>
+      <c r="E69" s="74" t="n"/>
+      <c r="F69" s="72" t="n"/>
     </row>
     <row r="70" ht="22" customHeight="1">
       <c r="B70" s="4" t="inlineStr">
@@ -1331,6 +2409,10 @@
           <t xml:space="preserve">  模拟10局AI vs AI：双方摧毁度都在20%~70%区间</t>
         </is>
       </c>
+      <c r="C70" s="74" t="n"/>
+      <c r="D70" s="74" t="n"/>
+      <c r="E70" s="74" t="n"/>
+      <c r="F70" s="72" t="n"/>
     </row>
     <row r="71" ht="22" customHeight="1">
       <c r="B71" s="4" t="inlineStr">
@@ -1338,6 +2420,10 @@
           <t xml:space="preserve">  胜率：攻守方各~50%（40%~60%）</t>
         </is>
       </c>
+      <c r="C71" s="74" t="n"/>
+      <c r="D71" s="74" t="n"/>
+      <c r="E71" s="74" t="n"/>
+      <c r="F71" s="72" t="n"/>
     </row>
     <row r="72" ht="22" customHeight="1">
       <c r="B72" s="4" t="inlineStr">
@@ -1345,6 +2431,10 @@
           <t xml:space="preserve">  0%摧毁度对局&lt;10%（不再出现打不进去的死局）</t>
         </is>
       </c>
+      <c r="C72" s="74" t="n"/>
+      <c r="D72" s="74" t="n"/>
+      <c r="E72" s="74" t="n"/>
+      <c r="F72" s="72" t="n"/>
     </row>
     <row r="73" ht="22" customHeight="1">
       <c r="B73" s="4" t="inlineStr">
@@ -1352,6 +2442,10 @@
           <t xml:space="preserve">  90%对局在150~210秒内结束</t>
         </is>
       </c>
+      <c r="C73" s="74" t="n"/>
+      <c r="D73" s="74" t="n"/>
+      <c r="E73" s="74" t="n"/>
+      <c r="F73" s="72" t="n"/>
     </row>
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
@@ -1371,11 +2465,13 @@
           <t>出场即向敌方大殿推进</t>
         </is>
       </c>
+      <c r="D77" s="72" t="n"/>
       <c r="E77" s="19" t="inlineStr">
         <is>
           <t>体修弟子(近战/费2) | 剑修弟子(远程/费3) | 御兽弟子(肉盾/费3)</t>
         </is>
       </c>
+      <c r="F77" s="72" t="n"/>
     </row>
     <row r="78" ht="30" customHeight="1">
       <c r="B78" s="18" t="inlineStr">
@@ -1388,11 +2484,13 @@
           <t>每5秒随机释放4分支技能</t>
         </is>
       </c>
+      <c r="D78" s="72" t="n"/>
       <c r="E78" s="19" t="inlineStr">
         <is>
           <t>金丹期长老(费6/血10) → 飞剑/丹药/符箓/御兽 随机</t>
         </is>
       </c>
+      <c r="F78" s="72" t="n"/>
     </row>
     <row r="79" ht="30" customHeight="1">
       <c r="B79" s="20" t="inlineStr">
@@ -1405,11 +2503,13 @@
           <t>布在阵法区/大殿前，不推进</t>
         </is>
       </c>
+      <c r="D79" s="72" t="n"/>
       <c r="E79" s="19" t="inlineStr">
         <is>
           <t>护山傀儡(肉盾/费3) | 护山灵兽(高血自爆/费4) | 护法长老(费6)</t>
         </is>
       </c>
+      <c r="F79" s="72" t="n"/>
     </row>
     <row r="80" ht="30" customHeight="1">
       <c r="B80" s="21" t="inlineStr">
@@ -1422,11 +2522,13 @@
           <t>布在阵法区格子，不动有血量</t>
         </is>
       </c>
+      <c r="D80" s="72" t="n"/>
       <c r="E80" s="19" t="inlineStr">
         <is>
           <t>截脉阵/寒霜阵/万刃阵/反震阵/天罗阵</t>
         </is>
       </c>
+      <c r="F80" s="72" t="n"/>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="B81" s="22" t="inlineStr">
@@ -1439,11 +2541,13 @@
           <t>需选目标，即时生效</t>
         </is>
       </c>
+      <c r="D81" s="72" t="n"/>
       <c r="E81" s="19" t="inlineStr">
         <is>
           <t>万剑归宗/五雷正法/御风诀/镇魂符/金钟罩/移山倒海/困仙索/天雷诀</t>
         </is>
       </c>
+      <c r="F81" s="72" t="n"/>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="23" t="inlineStr">
@@ -1496,6 +2600,7 @@
 验收：模拟10局摧毁度20~70%，真机60fps</t>
         </is>
       </c>
+      <c r="F85" s="72" t="n"/>
     </row>
     <row r="86" ht="48" customHeight="1">
       <c r="B86" s="25" t="inlineStr">
@@ -1519,6 +2624,7 @@
 验收：次留35%+，付费率3%+</t>
         </is>
       </c>
+      <c r="F86" s="72" t="n"/>
     </row>
     <row r="87" ht="48" customHeight="1">
       <c r="B87" s="25" t="inlineStr">
@@ -1542,6 +2648,7 @@
 验收：实时PvP延迟&lt;200ms，活跃占比60%+</t>
         </is>
       </c>
+      <c r="F87" s="72" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="106">
@@ -1552,8 +2659,8 @@
     <mergeCell ref="B80"/>
     <mergeCell ref="C79:D79"/>
     <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B58:F58"/>
     <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B58:F58"/>
     <mergeCell ref="E79:F79"/>
     <mergeCell ref="E87:F87"/>
     <mergeCell ref="C6:F6"/>
@@ -1656,7 +2763,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9535,7 +10642,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
